--- a/outputs/Factory_data_for_3PL_quote.xlsx
+++ b/outputs/Factory_data_for_3PL_quote.xlsx
@@ -975,7 +975,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Presentations in grey are our assumption from the product list; correct them if Bueno's pack differs.</t>
+          <t>Presentations in grey are our assumption from the product list; correct them if the factory's pack differs.</t>
         </is>
       </c>
     </row>
